--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inskulka\Suhas\Personal\IMP\ShreeRadhe\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB3304D-578E-4C49-887D-707D19F3404C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA061395-2560-4618-BFE0-9B68F588B901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{66D94E45-E37A-4FBF-905C-36C32A5F8617}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66D94E45-E37A-4FBF-905C-36C32A5F8617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>SKUID</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>hairloss, hairfall</t>
+  </si>
+  <si>
+    <t>sulphur 200</t>
+  </si>
+  <si>
+    <t>chronic skin conditions, digestive disorders, boosting overall immunity</t>
   </si>
 </sst>
 </file>
@@ -603,6 +609,24 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>200</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
       <c r="U4" t="s">
         <v>14</v>
       </c>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inskulka\Suhas\Personal\IMP\ShreeRadhe\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA061395-2560-4618-BFE0-9B68F588B901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27B8C74-7D5C-42A6-8537-06840F0902B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66D94E45-E37A-4FBF-905C-36C32A5F8617}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>SKUID</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>chronic skin conditions, digestive disorders, boosting overall immunity</t>
+  </si>
+  <si>
+    <t>SR10002</t>
   </si>
 </sst>
 </file>
@@ -609,6 +612,9 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inskulka\Suhas\Personal\IMP\ShreeRadhe\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27B8C74-7D5C-42A6-8537-06840F0902B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4716922-FE02-4021-851D-F29D3DDBC215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{66D94E45-E37A-4FBF-905C-36C32A5F8617}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{66D94E45-E37A-4FBF-905C-36C32A5F8617}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inskulka\Suhas\Personal\IMP\ShreeRadhe\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4716922-FE02-4021-851D-F29D3DDBC215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B98B274-EC2F-458F-95DD-B38876CF70B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{66D94E45-E37A-4FBF-905C-36C32A5F8617}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>SKUID</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>SR10002</t>
+  </si>
+  <si>
+    <t>SR10003</t>
+  </si>
+  <si>
+    <t>SR10004</t>
+  </si>
+  <si>
+    <t>SR10005</t>
   </si>
 </sst>
 </file>
@@ -638,17 +647,26 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
       <c r="U5" t="s">
         <v>15</v>
       </c>
       <c r="V5" s="1"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
       <c r="U6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
       <c r="U7" t="s">
         <v>17</v>
       </c>
